--- a/static/ruleTemplate.xlsx
+++ b/static/ruleTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Life Style\大创项目--数据质量管理\开发\Backend\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C097C00D-3513-451A-8391-A63DC8B2F508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12002A0B-4C3E-4AA1-AEA6-0189EC20AE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5220" yWindow="6250" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>表格名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -72,6 +72,14 @@
   </si>
   <si>
     <t>特征名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属域类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>评价域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -143,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -153,6 +161,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.25" customWidth="1"/>
@@ -445,7 +456,7 @@
     <col min="6" max="6" width="16.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -464,8 +475,11 @@
       <c r="F1" t="s">
         <v>2</v>
       </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" ht="53.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="53.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -483,6 +497,9 @@
       </c>
       <c r="F2" s="3" t="s">
         <v>7</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
